--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/VSnull</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -609,7 +609,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1489: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - PARASITE RPT STATUS (#63.05-15)</t>
+    <t>1489: terminologyMaps using null on MICROBIOLOGY - PARASITE RPT STATUS (#63.05-15)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ParasitologyReportStatus</t>
@@ -713,7 +713,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1528: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL</t>
+    <t>1528: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1814,7 +1814,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -1830,7 +1830,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="226.3125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="247.3984375" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSnull</t>
+    <t>http://va.gov/fhir/ValueSet/VSundefined</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSundefined</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1528: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
+    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1830,7 +1830,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="247.3984375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="598">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -892,9 +892,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
-  </si>
-  <si>
-    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -2242,7 +2239,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -5394,36 +5391,36 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AL25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AQ25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5544,10 +5541,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5670,10 +5667,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5696,19 +5693,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5757,7 +5754,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5772,22 +5769,22 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="AL28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5798,10 +5795,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5922,10 +5919,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6048,10 +6045,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6077,16 +6074,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6135,7 +6132,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6150,22 +6147,22 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6176,10 +6173,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6205,13 +6202,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6261,7 +6258,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6288,10 +6285,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6302,10 +6299,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6331,14 +6328,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6387,7 +6384,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6402,22 +6399,22 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6428,10 +6425,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6457,14 +6454,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6513,7 +6510,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6528,22 +6525,22 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6554,10 +6551,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6580,19 +6577,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6641,7 +6638,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6668,10 +6665,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6682,10 +6679,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6711,16 +6708,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6769,7 +6766,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6796,10 +6793,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6810,10 +6807,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6836,19 +6833,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6897,7 +6894,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6912,25 +6909,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6938,10 +6935,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6964,16 +6961,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7023,7 +7020,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7050,13 +7047,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7064,14 +7061,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7090,19 +7087,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7151,7 +7148,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7172,19 +7169,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AN39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AP39" t="s" s="2">
+      <c r="AQ39" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7192,14 +7189,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7218,19 +7215,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7267,7 +7264,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7277,7 +7274,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7286,31 +7283,31 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="AK40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7318,16 +7315,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C41" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="B41" t="s" s="2">
+      <c r="D41" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="D41" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7346,19 +7343,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7407,7 +7404,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7416,31 +7413,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AJ41" t="s" s="2">
+      <c r="AK41" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AK41" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AP41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7448,10 +7445,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7474,16 +7471,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7533,7 +7530,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7548,25 +7545,25 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AM42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7574,10 +7571,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7600,17 +7597,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7659,7 +7656,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7674,25 +7671,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AP43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7700,10 +7697,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7726,19 +7723,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7787,7 +7784,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7796,42 +7793,42 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AJ44" t="s" s="2">
+      <c r="AK44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AK44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AO44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR44" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7857,16 +7854,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7895,7 +7892,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7913,7 +7910,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7922,7 +7919,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7943,7 +7940,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7954,14 +7951,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7983,16 +7980,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8020,11 +8017,11 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8041,7 +8038,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8065,27 +8062,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AO46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AP46" t="s" s="2">
+      <c r="AQ46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR46" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AQ46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR46" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8108,19 +8105,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="N47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8169,7 +8166,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8184,22 +8181,22 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL47" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="AM47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8210,10 +8207,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8239,13 +8236,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8271,14 +8268,14 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="Y48" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="Y48" t="s" s="2">
+      <c r="Z48" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>468</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8295,7 +8292,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8319,27 +8316,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AP48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR48" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR48" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8365,16 +8362,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>474</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="N49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8399,14 +8396,14 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y49" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z49" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="Z49" t="s" s="2">
-        <v>479</v>
-      </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8423,7 +8420,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8450,10 +8447,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8464,10 +8461,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8490,16 +8487,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8549,7 +8546,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8564,36 +8561,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="AM50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>492</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8616,16 +8613,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8675,7 +8672,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8699,27 +8696,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>501</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8742,19 +8739,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8803,7 +8800,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8815,25 +8812,25 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AK52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8844,10 +8841,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8968,10 +8965,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9094,14 +9091,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9123,10 +9120,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9181,7 +9178,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9222,10 +9219,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9248,13 +9245,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9305,7 +9302,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9314,7 +9311,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9332,10 +9329,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9346,10 +9343,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9372,13 +9369,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>527</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9429,7 +9426,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9438,7 +9435,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9456,10 +9453,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9470,10 +9467,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9499,16 +9496,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9536,11 +9533,11 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>534</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9557,7 +9554,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9581,13 +9578,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9598,10 +9595,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9627,16 +9624,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9661,14 +9658,14 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>544</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9685,7 +9682,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9709,13 +9706,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>537</v>
-      </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9726,10 +9723,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9752,17 +9749,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9811,7 +9808,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9841,7 +9838,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9852,10 +9849,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9881,10 +9878,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9935,7 +9932,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9962,10 +9959,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9976,10 +9973,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10002,16 +9999,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10061,7 +10058,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10088,10 +10085,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10102,10 +10099,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10128,16 +10125,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10187,7 +10184,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10214,10 +10211,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10228,10 +10225,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10254,19 +10251,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>571</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>572</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10315,7 +10312,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10342,10 +10339,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10356,10 +10353,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10480,10 +10477,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10606,14 +10603,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10635,10 +10632,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10693,7 +10690,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10734,10 +10731,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10763,13 +10760,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>278</v>
@@ -10797,10 +10794,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>280</v>
@@ -10821,7 +10818,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10845,16 +10842,16 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -10862,10 +10859,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10888,19 +10885,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="O69" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10949,7 +10946,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10973,27 +10970,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AP69" t="s" s="2">
+      <c r="AQ69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR69" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR69" t="s" s="2">
-        <v>431</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11019,16 +11016,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>591</v>
       </c>
-      <c r="N70" t="s" s="2">
-        <v>592</v>
-      </c>
       <c r="O70" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11056,10 +11053,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11077,7 +11074,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11086,7 +11083,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11107,7 +11104,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11118,14 +11115,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11147,16 +11144,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11184,11 +11181,11 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z71" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z71" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11205,7 +11202,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11229,27 +11226,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AO71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AP71" t="s" s="2">
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>451</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11275,16 +11272,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="M72" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="N72" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O72" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11333,7 +11330,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11360,10 +11357,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1291,7 +1291,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1519,7 +1519,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$73</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2941" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -894,6 +894,9 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
+    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -1361,6 +1364,15 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>1857: source value from MICROBIOLOGY - PARASITE &gt; PARASITE - PARASITE &gt; ETIOLOGY FIELD - NAME (63.05-16 &gt; 63.34-.01 &gt; 61.2-.01)</t>
+  </si>
+  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1382,6 +1394,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -2201,7 +2216,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR72"/>
+  <dimension ref="A1:AR73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -2239,7 +2254,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -5391,36 +5406,36 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5541,10 +5556,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5667,10 +5682,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5693,19 +5708,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5754,7 +5769,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5769,7 +5784,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5781,10 +5796,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5795,10 +5810,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5919,10 +5934,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6045,10 +6060,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6074,16 +6089,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6132,7 +6147,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6147,7 +6162,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6159,10 +6174,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6173,10 +6188,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6202,13 +6217,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6258,7 +6273,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6285,10 +6300,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6299,10 +6314,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6328,14 +6343,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6384,7 +6399,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6399,7 +6414,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6411,10 +6426,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6425,10 +6440,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6454,14 +6469,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6510,7 +6525,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6525,7 +6540,7 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6537,10 +6552,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6551,10 +6566,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6577,19 +6592,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6638,7 +6653,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6665,10 +6680,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6679,10 +6694,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6708,16 +6723,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6766,7 +6781,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6793,10 +6808,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6807,10 +6822,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6833,19 +6848,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6894,7 +6909,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6909,25 +6924,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6935,10 +6950,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6961,16 +6976,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7020,7 +7035,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7047,13 +7062,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7061,14 +7076,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7087,19 +7102,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7148,7 +7163,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7169,19 +7184,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7189,14 +7204,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7215,19 +7230,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7264,7 +7279,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7274,7 +7289,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7283,10 +7298,10 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7295,19 +7310,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7315,16 +7330,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7343,19 +7358,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7404,7 +7419,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7413,31 +7428,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7445,10 +7460,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7471,16 +7486,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7530,7 +7545,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7545,10 +7560,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7557,13 +7572,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7571,10 +7586,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7597,17 +7612,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7656,7 +7671,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7671,25 +7686,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7697,10 +7712,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7723,19 +7738,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7772,19 +7787,17 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7793,10 +7806,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7808,29 +7821,31 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7848,22 +7863,22 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7888,11 +7903,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>436</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7910,7 +7927,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7919,13 +7936,13 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>427</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -7934,41 +7951,41 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>84</v>
+        <v>428</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>137</v>
+        <v>429</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -7980,16 +7997,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8016,11 +8033,9 @@
       <c r="X46" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y46" t="s" s="2">
-        <v>445</v>
-      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8038,22 +8053,22 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>442</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>84</v>
@@ -8062,31 +8077,31 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>448</v>
+        <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8096,7 +8111,7 @@
         <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>84</v>
@@ -8105,19 +8120,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>452</v>
+        <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8142,13 +8157,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8166,7 +8181,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8181,36 +8196,36 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>457</v>
+        <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8221,10 +8236,10 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>84</v>
@@ -8233,18 +8248,20 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>457</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8268,13 +8285,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8292,13 +8309,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8307,36 +8324,36 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>471</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8362,17 +8379,15 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8396,13 +8411,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8420,7 +8435,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8444,27 +8459,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>84</v>
+        <v>473</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8478,7 +8493,7 @@
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
@@ -8487,18 +8502,20 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>482</v>
+        <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>480</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8522,13 +8539,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8546,7 +8563,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8561,36 +8578,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>491</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8604,7 +8621,7 @@
         <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>84</v>
@@ -8613,16 +8630,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8672,7 +8689,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8687,36 +8704,36 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>84</v>
+        <v>491</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>492</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8727,7 +8744,7 @@
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
@@ -8739,20 +8756,18 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8800,19 +8815,19 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>507</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8824,27 +8839,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>84</v>
+        <v>502</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
+        <v>505</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8855,7 +8870,7 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -8867,16 +8882,20 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>161</v>
+        <v>507</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>162</v>
+        <v>508</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8924,19 +8943,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>164</v>
+        <v>506</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>84</v>
+        <v>512</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8951,10 +8970,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>84</v>
+        <v>513</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>165</v>
+        <v>514</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8965,21 +8984,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -8991,17 +9010,15 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9050,19 +9067,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9091,14 +9108,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>513</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9111,26 +9128,24 @@
         <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>514</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>515</v>
+        <v>167</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9178,7 +9193,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>516</v>
+        <v>171</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9208,7 +9223,7 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9226,26 +9241,26 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>84</v>
+        <v>518</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>518</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
         <v>519</v>
@@ -9253,8 +9268,12 @@
       <c r="M56" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+      <c r="N56" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9302,19 +9321,19 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -9329,10 +9348,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>523</v>
+        <v>137</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9343,10 +9362,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9369,13 +9388,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9426,7 +9445,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9435,7 +9454,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9453,10 +9472,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9467,10 +9486,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9493,20 +9512,16 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>183</v>
+        <v>523</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="N58" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="O58" t="s" s="2">
-        <v>532</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9530,13 +9545,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>534</v>
+        <v>84</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9554,7 +9569,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9563,7 +9578,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>84</v>
+        <v>526</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9578,13 +9593,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>535</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>449</v>
+        <v>532</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9595,10 +9610,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9609,7 +9624,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -9624,16 +9639,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9658,13 +9673,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>465</v>
+        <v>118</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9682,13 +9697,13 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
@@ -9706,13 +9721,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9723,10 +9738,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9737,7 +9752,7 @@
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
@@ -9749,17 +9764,19 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9784,13 +9801,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>84</v>
+        <v>547</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>84</v>
+        <v>548</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9808,13 +9825,13 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
@@ -9832,13 +9849,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>84</v>
+        <v>540</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>549</v>
+        <v>454</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9849,10 +9866,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9875,7 +9892,7 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>161</v>
+        <v>550</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>551</v>
@@ -9884,7 +9901,9 @@
         <v>552</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9932,7 +9951,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9959,10 +9978,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9973,10 +9992,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9987,7 +10006,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -9996,10 +10015,10 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>555</v>
+        <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>556</v>
@@ -10007,9 +10026,7 @@
       <c r="M62" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="N62" t="s" s="2">
-        <v>558</v>
-      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10058,13 +10075,13 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
@@ -10085,10 +10102,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>559</v>
+        <v>527</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10099,10 +10116,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10125,16 +10142,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>565</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10184,7 +10201,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10211,10 +10228,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10225,10 +10242,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10251,7 +10268,7 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>502</v>
+        <v>567</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>568</v>
@@ -10262,9 +10279,7 @@
       <c r="N64" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>571</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10312,7 +10327,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10339,10 +10354,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10353,10 +10368,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10367,7 +10382,7 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10376,19 +10391,23 @@
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>161</v>
+        <v>507</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>162</v>
+        <v>573</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10436,19 +10455,19 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>164</v>
+        <v>572</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10463,10 +10482,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>84</v>
+        <v>577</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>165</v>
+        <v>578</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10477,21 +10496,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
@@ -10503,17 +10522,15 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10562,19 +10579,19 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10603,14 +10620,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>513</v>
+        <v>139</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10623,26 +10640,24 @@
         <v>84</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>141</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>167</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O67" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10690,7 +10705,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>171</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10720,7 +10735,7 @@
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10731,45 +10746,45 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>84</v>
+        <v>518</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J68" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>578</v>
+        <v>519</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>579</v>
+        <v>520</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>580</v>
+        <v>143</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>278</v>
+        <v>149</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10794,13 +10809,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>581</v>
+        <v>84</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>280</v>
+        <v>84</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10818,19 +10833,19 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>577</v>
+        <v>521</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -10842,16 +10857,16 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>284</v>
+        <v>137</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -10859,10 +10874,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10870,7 +10885,7 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G69" t="s" s="2">
         <v>94</v>
@@ -10885,19 +10900,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>420</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>586</v>
-      </c>
       <c r="O69" t="s" s="2">
-        <v>424</v>
+        <v>278</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10922,13 +10937,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>586</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10946,10 +10961,10 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>94</v>
@@ -10973,16 +10988,16 @@
         <v>587</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>428</v>
+        <v>284</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>429</v>
+        <v>285</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>84</v>
+        <v>286</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -11010,10 +11025,10 @@
         <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>183</v>
+        <v>421</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>589</v>
@@ -11025,7 +11040,7 @@
         <v>591</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11050,13 +11065,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>592</v>
+        <v>84</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>436</v>
+        <v>84</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11083,7 +11098,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>593</v>
+        <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11098,38 +11113,38 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>84</v>
+        <v>592</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>137</v>
+        <v>429</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11144,16 +11159,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>441</v>
+        <v>594</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>442</v>
+        <v>595</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>443</v>
+        <v>596</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11181,10 +11196,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>445</v>
+        <v>597</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11202,16 +11217,16 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>84</v>
+        <v>598</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11226,31 +11241,31 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>448</v>
+        <v>137</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11269,19 +11284,19 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>596</v>
+        <v>446</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>597</v>
+        <v>447</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>505</v>
+        <v>448</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>506</v>
+        <v>449</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11306,13 +11321,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11330,7 +11345,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11354,23 +11369,151 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>508</v>
+        <v>453</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>509</v>
+        <v>454</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR73" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR72">
+  <autoFilter ref="A1:AR73">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11380,7 +11523,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI72">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1396,7 +1396,7 @@
 us-core-2</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2031: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
   </si>
   <si>
     <t>1489: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - PARASITE RPT STATUS (63.05-15)</t>
@@ -2244,7 +2244,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="605">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -894,7 +894,11 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t>1528: fixed value = http://loinc.org#42807-8 Parasite identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+LabObservationMicrobiologyParasitologyObservation-1528:if NULL then fixed value http://loinc.org#42807-8 "Parasite identified in Isolate" {null}</t>
+  </si>
+  <si>
+    <t>1528: fixed value = http://loinc.org#42807-8 "Parasite identified in Isolate" when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -974,6 +978,10 @@
   </si>
   <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+LabObservationMicrobiologyParasitologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
@@ -5403,39 +5411,39 @@
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>281</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5556,10 +5564,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5682,10 +5690,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5708,19 +5716,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5769,7 +5777,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5784,7 +5792,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5796,10 +5804,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5810,10 +5818,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5934,10 +5942,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6060,10 +6068,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6089,16 +6097,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6147,7 +6155,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6159,10 +6167,10 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>309</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6174,10 +6182,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6188,10 +6196,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6217,13 +6225,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6273,7 +6281,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6300,10 +6308,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6314,10 +6322,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6343,14 +6351,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6399,7 +6407,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6414,7 +6422,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6426,10 +6434,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6440,10 +6448,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6469,14 +6477,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6525,7 +6533,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6540,7 +6548,7 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6552,10 +6560,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6566,10 +6574,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6592,19 +6600,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6653,7 +6661,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6680,10 +6688,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6694,10 +6702,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6723,16 +6731,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6781,7 +6789,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6808,10 +6816,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6822,10 +6830,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6848,19 +6856,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6909,7 +6917,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6924,25 +6932,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6950,10 +6958,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6976,16 +6984,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7035,7 +7043,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7062,13 +7070,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7076,14 +7084,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7102,19 +7110,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7163,7 +7171,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7184,19 +7192,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7204,14 +7212,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7230,19 +7238,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7279,7 +7287,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7289,7 +7297,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7298,10 +7306,10 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7310,19 +7318,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7330,16 +7338,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7358,19 +7366,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7419,7 +7427,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7428,31 +7436,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7460,10 +7468,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7486,16 +7494,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7545,7 +7553,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7560,10 +7568,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7572,13 +7580,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7586,10 +7594,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7612,17 +7620,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7671,7 +7679,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7686,25 +7694,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7712,10 +7720,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7738,19 +7746,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7787,7 +7795,7 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7797,7 +7805,7 @@
         <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7806,10 +7814,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7821,30 +7829,30 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -7869,16 +7877,16 @@
         <v>161</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7927,7 +7935,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7936,13 +7944,13 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -7951,27 +7959,27 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7997,16 +8005,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8035,7 +8043,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8053,7 +8061,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8062,13 +8070,13 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>84</v>
@@ -8083,7 +8091,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8094,14 +8102,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8123,16 +8131,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8160,10 +8168,10 @@
         <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8181,7 +8189,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8205,27 +8213,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8248,19 +8256,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8309,7 +8317,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8324,10 +8332,10 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
@@ -8336,10 +8344,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8350,10 +8358,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8379,13 +8387,13 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8411,13 +8419,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8435,7 +8443,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8459,27 +8467,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8505,16 +8513,16 @@
         <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8539,13 +8547,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8563,7 +8571,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8590,10 +8598,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8604,10 +8612,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8630,16 +8638,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8689,7 +8697,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8704,36 +8712,36 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8756,16 +8764,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8815,7 +8823,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8839,27 +8847,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8882,19 +8890,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8943,7 +8951,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8955,7 +8963,7 @@
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8970,10 +8978,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8984,10 +8992,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9108,10 +9116,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9234,14 +9242,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9263,10 +9271,10 @@
         <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>143</v>
@@ -9321,7 +9329,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9362,10 +9370,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9388,13 +9396,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9445,7 +9453,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9454,7 +9462,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9472,10 +9480,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9486,10 +9494,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9512,13 +9520,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9569,7 +9577,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9578,7 +9586,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9596,10 +9604,10 @@
         <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9610,10 +9618,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9639,16 +9647,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9676,10 +9684,10 @@
         <v>118</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9697,7 +9705,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9721,13 +9729,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9738,10 +9746,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9767,16 +9775,16 @@
         <v>183</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9801,13 +9809,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9825,7 +9833,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9849,13 +9857,13 @@
         <v>84</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9866,10 +9874,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9892,17 +9900,17 @@
         <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9951,7 +9959,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9981,7 +9989,7 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9992,10 +10000,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10021,10 +10029,10 @@
         <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10075,7 +10083,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10102,10 +10110,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10116,10 +10124,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10142,16 +10150,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10201,7 +10209,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10228,10 +10236,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10242,10 +10250,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10268,16 +10276,16 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10327,7 +10335,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10354,10 +10362,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10368,10 +10376,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10394,19 +10402,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10455,7 +10463,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10482,10 +10490,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10496,10 +10504,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10620,10 +10628,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10746,14 +10754,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10775,10 +10783,10 @@
         <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>143</v>
@@ -10833,7 +10841,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10874,10 +10882,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10903,13 +10911,13 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>278</v>
@@ -10937,10 +10945,10 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="Z69" t="s" s="2">
         <v>280</v>
@@ -10961,7 +10969,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -10985,16 +10993,16 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>84</v>
@@ -11002,10 +11010,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11028,19 +11036,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11089,7 +11097,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11113,27 +11121,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11159,16 +11167,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11196,10 +11204,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11217,7 +11225,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11226,7 +11234,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11247,7 +11255,7 @@
         <v>137</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11258,14 +11266,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11287,16 +11295,16 @@
         <v>183</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11324,10 +11332,10 @@
         <v>188</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11345,7 +11353,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11369,27 +11377,27 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR72" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11415,16 +11423,16 @@
         <v>85</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11473,7 +11481,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11500,10 +11508,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -895,7 +895,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-LabObservationMicrobiologyParasitologyObservation-1528:if NULL then fixed value http://loinc.org#42807-8 "Parasite identified in Isolate" {null}</t>
+lompo-49-1528:63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-: if NULL then http://loinc.org#42807-8 "Parasite identified in Isolate" {null}</t>
   </si>
   <si>
     <t>1528: fixed value = http://loinc.org#42807-8 "Parasite identified in Isolate" when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
@@ -981,7 +981,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-LabObservationMicrobiologyParasitologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
+lompo-49-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1142,7 +1142,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2271,7 +2271,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -807,6 +807,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.ParasitologyReportStatus</t>
+  </si>
+  <si>
+    <t>Documents.DocumentCompletionStatus,LabOrder.Result.ResultStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1142,8 +1145,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1297,6 +1299,9 @@
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
   </si>
   <si>
+    <t>Documents.ToTime,LabOrder.Result.ResultTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1328,6 +1333,9 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
+    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1566,6 +1574,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
+  </si>
+  <si>
+    <t>LabOrder.ResultExtension.GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2271,7 +2282,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -5107,22 +5118,22 @@
         <v>254</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -5130,10 +5141,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5159,16 +5170,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -5178,7 +5189,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5196,16 +5207,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5215,7 +5226,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5230,7 +5241,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5248,10 +5259,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5259,13 +5270,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5290,16 +5301,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5309,7 +5320,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5327,10 +5338,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5348,7 +5359,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5381,10 +5392,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5392,14 +5403,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5421,16 +5432,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5458,10 +5469,10 @@
         <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5479,7 +5490,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5491,10 +5502,10 @@
         <v>85</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>85</v>
@@ -5503,30 +5514,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5650,10 +5661,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5779,10 +5790,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5805,19 +5816,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5866,7 +5877,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5881,7 +5892,7 @@
         <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -5896,10 +5907,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5910,10 +5921,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6037,10 +6048,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6166,10 +6177,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6195,16 +6206,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6253,7 +6264,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6265,10 +6276,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6283,10 +6294,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6297,10 +6308,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6326,13 +6337,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6382,7 +6393,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6412,10 +6423,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6426,10 +6437,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6455,14 +6466,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6511,7 +6522,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6526,7 +6537,7 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6541,10 +6552,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6555,10 +6566,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6584,14 +6595,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6640,7 +6651,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6655,7 +6666,7 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6670,10 +6681,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6684,10 +6695,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6710,19 +6721,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6771,7 +6782,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6801,10 +6812,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6815,10 +6826,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6844,16 +6855,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6902,7 +6913,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6932,10 +6943,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -6946,10 +6957,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6972,19 +6983,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7033,7 +7044,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7048,28 +7059,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7077,10 +7088,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7103,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7162,7 +7173,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7192,13 +7203,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7206,14 +7217,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7232,19 +7243,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7293,7 +7304,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7317,19 +7328,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7337,14 +7348,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7363,19 +7374,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7412,7 +7423,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7422,7 +7433,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7431,10 +7442,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7446,19 +7457,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7466,16 +7477,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7494,19 +7505,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7555,7 +7566,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7564,34 +7575,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7599,10 +7610,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7625,16 +7636,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7684,7 +7695,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7699,13 +7710,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>85</v>
+        <v>411</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7714,13 +7725,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7728,10 +7739,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7754,17 +7765,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7813,7 +7824,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7828,28 +7839,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>85</v>
+        <v>422</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7857,10 +7868,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7883,19 +7894,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7932,7 +7943,7 @@
         <v>85</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7942,7 +7953,7 @@
         <v>171</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7951,10 +7962,10 @@
         <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -7969,30 +7980,30 @@
         <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8017,16 +8028,16 @@
         <v>162</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8075,7 +8086,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8084,45 +8095,45 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AR45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS45" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AR45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS45" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8148,16 +8159,16 @@
         <v>184</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8186,7 +8197,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8204,7 +8215,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8213,13 +8224,13 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>85</v>
@@ -8237,7 +8248,7 @@
         <v>138</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
@@ -8248,14 +8259,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8277,16 +8288,16 @@
         <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8314,10 +8325,10 @@
         <v>189</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8335,7 +8346,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8362,27 +8373,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8405,19 +8416,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8466,7 +8477,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8481,10 +8492,10 @@
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>85</v>
@@ -8496,10 +8507,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8510,10 +8521,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8539,13 +8550,13 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8571,13 +8582,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8595,7 +8606,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8622,27 +8633,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8668,16 +8679,16 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8702,13 +8713,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8726,7 +8737,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8756,10 +8767,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8770,10 +8781,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8796,16 +8807,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8855,7 +8866,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8870,39 +8881,39 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8925,16 +8936,16 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8984,7 +8995,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9011,27 +9022,27 @@
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9054,19 +9065,19 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9115,7 +9126,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9127,7 +9138,7 @@
         <v>85</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>85</v>
@@ -9145,10 +9156,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -9159,10 +9170,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9286,10 +9297,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9415,14 +9426,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9444,10 +9455,10 @@
         <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>144</v>
@@ -9502,7 +9513,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9546,10 +9557,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9572,13 +9583,13 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9629,7 +9640,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9638,7 +9649,7 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
@@ -9659,10 +9670,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9673,10 +9684,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9699,13 +9710,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9756,7 +9767,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9765,7 +9776,7 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>107</v>
@@ -9786,10 +9797,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9800,10 +9811,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9829,16 +9840,16 @@
         <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9866,10 +9877,10 @@
         <v>119</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -9887,7 +9898,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9914,13 +9925,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9931,10 +9942,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9960,16 +9971,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -9994,13 +10005,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10018,7 +10029,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10045,13 +10056,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10062,10 +10073,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10088,17 +10099,17 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -10147,7 +10158,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10180,7 +10191,7 @@
         <v>85</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10191,10 +10202,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10220,10 +10231,10 @@
         <v>162</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10274,7 +10285,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10304,10 +10315,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10318,10 +10329,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10344,16 +10355,16 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10403,7 +10414,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10433,10 +10444,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10447,10 +10458,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10473,16 +10484,16 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10532,7 +10543,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10562,10 +10573,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10576,10 +10587,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10602,19 +10613,19 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10663,7 +10674,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10693,10 +10704,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10707,10 +10718,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10834,10 +10845,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10963,14 +10974,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10992,10 +11003,10 @@
         <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>144</v>
@@ -11050,7 +11061,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11094,10 +11105,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11123,16 +11134,16 @@
         <v>184</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11157,31 +11168,31 @@
         <v>85</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>95</v>
@@ -11208,16 +11219,16 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AS69" t="s" s="2">
         <v>85</v>
@@ -11225,10 +11236,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11251,19 +11262,19 @@
         <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11312,7 +11323,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11339,27 +11350,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11385,16 +11396,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11422,28 +11433,28 @@
         <v>189</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11452,7 +11463,7 @@
         <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>107</v>
@@ -11476,7 +11487,7 @@
         <v>138</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11487,14 +11498,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11516,16 +11527,16 @@
         <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11553,10 +11564,10 @@
         <v>189</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11574,7 +11585,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11601,27 +11612,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11647,16 +11658,16 @@
         <v>86</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11705,7 +11716,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -11735,10 +11746,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1145,7 +1145,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1333,7 +1333,7 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
-    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+    <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1576,7 +1576,7 @@
     <t>Micro.Microbiology.MicrobiologyAccession</t>
   </si>
   <si>
-    <t>LabOrder.ResultExtension.GroupName</t>
+    <t>LabOrder.Extension[ResultExtension].GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2282,7 +2282,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="620">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1314,7 +1314,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1327,6 +1327,47 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-at</t>
+  </si>
+  <si>
+    <t>va-at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
+</t>
+  </si>
+  <si>
+    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
+  </si>
+  <si>
+    <t>Documents.EnteredAt,LabOrder.Result.EnteredAt</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-by</t>
+  </si>
+  <si>
+    <t>va-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+</t>
+  </si>
+  <si>
     <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
@@ -1334,18 +1375,6 @@
   </si>
   <si>
     <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2242,7 +2271,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS73"/>
+  <dimension ref="A1:AS75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -7756,7 +7785,7 @@
         <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>85</v>
@@ -7812,16 +7841,14 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>415</v>
@@ -7839,28 +7866,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AR43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7868,12 +7895,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
       </c>
@@ -7894,19 +7923,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -7943,67 +7970,69 @@
         <v>85</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>428</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>85</v>
+        <v>429</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>435</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>438</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8025,19 +8054,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>162</v>
+        <v>432</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8086,54 +8113,54 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AJ45" t="s" s="2">
+      <c r="AL45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AK45" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AM45" t="s" s="2">
-        <v>85</v>
+        <v>435</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>435</v>
+        <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>85</v>
+        <v>423</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>438</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8153,22 +8180,22 @@
         <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>184</v>
+        <v>437</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8193,29 +8220,29 @@
         <v>85</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y46" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z46" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8224,13 +8251,13 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>107</v>
+        <v>443</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>449</v>
+        <v>85</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>85</v>
@@ -8242,62 +8269,64 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>85</v>
+        <v>444</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>138</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>85</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8322,13 +8351,13 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>457</v>
+        <v>85</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>458</v>
+        <v>85</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8346,22 +8375,22 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>442</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>107</v>
+        <v>443</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8373,27 +8402,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8404,7 +8433,7 @@
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>96</v>
@@ -8416,19 +8445,19 @@
         <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>464</v>
+        <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8453,13 +8482,11 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8477,25 +8504,25 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>85</v>
+        <v>457</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>470</v>
+        <v>85</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>85</v>
@@ -8507,10 +8534,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>471</v>
+        <v>138</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8521,21 +8548,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>85</v>
@@ -8550,15 +8577,17 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8582,13 +8611,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>477</v>
+        <v>189</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8606,13 +8635,13 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>85</v>
@@ -8633,27 +8662,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8664,10 +8693,10 @@
         <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8676,19 +8705,19 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>184</v>
+        <v>473</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8713,13 +8742,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>477</v>
+        <v>85</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>489</v>
+        <v>85</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8737,13 +8766,13 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>85</v>
@@ -8752,10 +8781,10 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>85</v>
+        <v>478</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>85</v>
@@ -8767,10 +8796,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8781,10 +8810,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8798,7 +8827,7 @@
         <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>85</v>
@@ -8807,16 +8836,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>494</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8842,13 +8871,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>85</v>
+        <v>488</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8866,7 +8895,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8881,39 +8910,39 @@
         <v>107</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>499</v>
+        <v>85</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>504</v>
+        <v>492</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8936,18 +8965,20 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>506</v>
+        <v>184</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>496</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>497</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -8971,13 +9002,13 @@
         <v>85</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>85</v>
+        <v>498</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>85</v>
+        <v>499</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>85</v>
@@ -8995,7 +9026,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9022,27 +9053,27 @@
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>510</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>513</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9053,10 +9084,10 @@
         <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>85</v>
@@ -9065,20 +9096,18 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>85</v>
       </c>
@@ -9126,54 +9155,54 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>520</v>
+        <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>85</v>
+        <v>507</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>85</v>
+        <v>508</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>85</v>
+        <v>509</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>85</v>
+        <v>513</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9196,15 +9225,17 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>162</v>
+        <v>515</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>163</v>
+        <v>516</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9253,7 +9284,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>165</v>
+        <v>514</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9265,7 +9296,7 @@
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9280,31 +9311,31 @@
         <v>85</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>85</v>
+        <v>519</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>85</v>
+        <v>520</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>166</v>
+        <v>521</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>85</v>
+        <v>522</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9323,18 +9354,20 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>141</v>
+        <v>524</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>142</v>
+        <v>525</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>168</v>
+        <v>526</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9382,7 +9415,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>172</v>
+        <v>523</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9394,7 +9427,7 @@
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>146</v>
+        <v>529</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>85</v>
@@ -9412,10 +9445,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>166</v>
+        <v>531</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9426,46 +9459,42 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>527</v>
+        <v>163</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
       </c>
@@ -9513,19 +9542,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>529</v>
+        <v>165</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9546,7 +9575,7 @@
         <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9557,21 +9586,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>85</v>
@@ -9583,15 +9612,17 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>531</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>532</v>
+        <v>142</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9640,19 +9671,19 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>530</v>
+        <v>172</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>534</v>
+        <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9670,10 +9701,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>535</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>536</v>
+        <v>166</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9684,42 +9715,46 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>531</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9767,19 +9802,19 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>534</v>
+        <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9797,10 +9832,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>535</v>
+        <v>85</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>540</v>
+        <v>138</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9811,10 +9846,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9837,20 +9872,16 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>184</v>
+        <v>540</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>542</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>545</v>
-      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
       </c>
@@ -9874,13 +9905,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>546</v>
+        <v>85</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -9898,7 +9929,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9907,7 +9938,7 @@
         <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -9925,13 +9956,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>548</v>
+        <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>461</v>
+        <v>545</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9942,10 +9973,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9956,7 +9987,7 @@
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
@@ -9968,20 +9999,16 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>184</v>
+        <v>540</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>85</v>
       </c>
@@ -10005,13 +10032,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>477</v>
+        <v>85</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10029,16 +10056,16 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>107</v>
@@ -10056,13 +10083,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>548</v>
+        <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AQ60" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10073,10 +10100,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10099,17 +10126,19 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>558</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>553</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -10134,13 +10163,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>555</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>556</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10158,7 +10187,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10185,13 +10214,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>85</v>
+        <v>558</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>562</v>
+        <v>470</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10202,10 +10231,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10216,7 +10245,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10228,16 +10257,20 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10261,13 +10294,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>85</v>
+        <v>564</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10285,13 +10318,13 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>85</v>
@@ -10312,13 +10345,13 @@
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>535</v>
+        <v>558</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>566</v>
+        <v>470</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10329,10 +10362,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10343,7 +10376,7 @@
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>85</v>
@@ -10352,21 +10385,21 @@
         <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
@@ -10414,13 +10447,13 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>85</v>
@@ -10444,10 +10477,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>572</v>
+        <v>85</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10458,10 +10491,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10472,7 +10505,7 @@
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>85</v>
@@ -10481,20 +10514,18 @@
         <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>575</v>
+        <v>162</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10543,13 +10574,13 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>85</v>
@@ -10573,10 +10604,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10587,10 +10618,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10613,20 +10644,18 @@
         <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>515</v>
+        <v>577</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10674,7 +10703,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10704,10 +10733,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10718,10 +10747,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10732,7 +10761,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10741,18 +10770,20 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>162</v>
+        <v>584</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>163</v>
+        <v>585</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>586</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>587</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10801,19 +10832,19 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>165</v>
+        <v>583</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>85</v>
@@ -10831,10 +10862,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>166</v>
+        <v>588</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10845,14 +10876,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10868,21 +10899,23 @@
         <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>524</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>142</v>
+        <v>590</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>168</v>
+        <v>591</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -10930,7 +10963,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>172</v>
+        <v>589</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -10942,7 +10975,7 @@
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -10960,10 +10993,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>166</v>
+        <v>595</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -10974,46 +11007,42 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>527</v>
+        <v>163</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11061,19 +11090,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>529</v>
+        <v>165</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11094,7 +11123,7 @@
         <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11105,21 +11134,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>85</v>
@@ -11128,23 +11157,21 @@
         <v>85</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>591</v>
+        <v>142</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>592</v>
+        <v>168</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11168,13 +11195,13 @@
         <v>85</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>477</v>
+        <v>85</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>594</v>
+        <v>85</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>85</v>
@@ -11192,19 +11219,19 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>590</v>
+        <v>172</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11219,16 +11246,16 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>595</v>
+        <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>288</v>
+        <v>166</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>289</v>
+        <v>85</v>
       </c>
       <c r="AS69" t="s" s="2">
         <v>85</v>
@@ -11236,45 +11263,45 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>428</v>
+        <v>141</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>597</v>
+        <v>536</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>598</v>
+        <v>537</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>599</v>
+        <v>144</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>432</v>
+        <v>150</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11323,19 +11350,19 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>596</v>
+        <v>538</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11350,27 +11377,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>437</v>
+        <v>138</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>438</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11378,7 +11405,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>95</v>
@@ -11390,22 +11417,22 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="O71" t="s" s="2">
-        <v>446</v>
+        <v>280</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11430,13 +11457,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>189</v>
+        <v>486</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>447</v>
+        <v>282</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11454,16 +11481,16 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>606</v>
+        <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>107</v>
@@ -11481,16 +11508,16 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>138</v>
+        <v>287</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>450</v>
+        <v>288</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>85</v>
+        <v>289</v>
       </c>
       <c r="AS71" t="s" s="2">
         <v>85</v>
@@ -11498,21 +11525,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -11521,22 +11548,22 @@
         <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>184</v>
+        <v>437</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>453</v>
+        <v>606</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>454</v>
+        <v>607</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>455</v>
+        <v>608</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11561,13 +11588,13 @@
         <v>85</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>457</v>
+        <v>85</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>458</v>
+        <v>85</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11585,13 +11612,13 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
@@ -11612,27 +11639,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>459</v>
+        <v>609</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11643,7 +11670,7 @@
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -11655,19 +11682,19 @@
         <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>518</v>
+        <v>613</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>519</v>
+        <v>455</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11692,13 +11719,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11716,16 +11743,16 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>107</v>
@@ -11746,20 +11773,282 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>521</v>
+        <v>138</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>522</v>
+        <v>459</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS74" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS75" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS73">
+  <autoFilter ref="A1:AS75">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11769,7 +12058,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI72">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$77</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="628">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1327,6 +1327,10 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1423,6 +1427,28 @@
   </si>
   <si>
     <t>1857: source value from MICROBIOLOGY - PARASITE &gt; PARASITE - PARASITE &gt; ETIOLOGY FIELD - NAME (63.05-16 &gt; 63.34-.01 &gt; 61.2-.01)</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>2099: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>2100: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2271,12 +2297,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS75"/>
+  <dimension ref="A1:AS77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -7841,7 +7867,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>269</v>
+        <v>420</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7875,19 +7901,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7895,13 +7921,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>415</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7923,7 +7949,7 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>417</v>
@@ -7997,28 +8023,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8026,13 +8052,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>415</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8054,7 +8080,7 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>417</v>
@@ -8128,28 +8154,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8157,10 +8183,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8183,19 +8209,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8242,7 +8268,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8251,10 +8277,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8269,30 +8295,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8317,16 +8343,16 @@
         <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8375,7 +8401,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8384,13 +8410,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8402,29 +8428,31 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="D48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8442,22 +8470,22 @@
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>184</v>
+        <v>454</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8482,11 +8510,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>456</v>
+        <v>85</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8504,7 +8534,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>451</v>
+        <v>437</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8513,13 +8543,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>444</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8531,62 +8561,64 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>85</v>
+        <v>445</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>138</v>
+        <v>446</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>85</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8611,13 +8643,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>466</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>467</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8635,22 +8667,22 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>460</v>
+        <v>437</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>444</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>85</v>
+        <v>458</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8662,27 +8694,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>471</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8693,7 +8725,7 @@
         <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>96</v>
@@ -8705,19 +8737,19 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>473</v>
+        <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8742,13 +8774,11 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>85</v>
+        <v>464</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8766,25 +8796,25 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>85</v>
+        <v>465</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>479</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>85</v>
@@ -8796,10 +8826,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>480</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8810,21 +8840,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>85</v>
+        <v>469</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8839,15 +8869,17 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>472</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8871,13 +8903,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>486</v>
+        <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8895,13 +8927,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -8922,27 +8954,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>492</v>
+        <v>479</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8953,10 +8985,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -8965,19 +8997,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>184</v>
+        <v>481</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9002,13 +9034,13 @@
         <v>85</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>486</v>
+        <v>85</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>499</v>
+        <v>85</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>85</v>
@@ -9026,13 +9058,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9041,10 +9073,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>85</v>
+        <v>487</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9056,10 +9088,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9070,10 +9102,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9087,7 +9119,7 @@
         <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>85</v>
@@ -9096,16 +9128,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>503</v>
+        <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9131,13 +9163,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>85</v>
+        <v>495</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>85</v>
+        <v>496</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9155,7 +9187,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9170,39 +9202,39 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>507</v>
+        <v>85</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>509</v>
+        <v>85</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9225,18 +9257,20 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>515</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9260,13 +9294,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>85</v>
+        <v>506</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>85</v>
+        <v>507</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9284,7 +9318,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9311,27 +9345,27 @@
         <v>85</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>522</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9342,10 +9376,10 @@
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9354,20 +9388,18 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9415,54 +9447,54 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>529</v>
+        <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>85</v>
+        <v>516</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>85</v>
+        <v>517</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>85</v>
+        <v>518</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>85</v>
+        <v>521</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9485,15 +9517,17 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>162</v>
+        <v>523</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>163</v>
+        <v>524</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9542,7 +9576,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>165</v>
+        <v>522</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9554,7 +9588,7 @@
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9569,31 +9603,31 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>85</v>
+        <v>528</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>166</v>
+        <v>529</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9612,18 +9646,20 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>532</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>142</v>
+        <v>533</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>168</v>
+        <v>534</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>536</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9671,7 +9707,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>172</v>
+        <v>531</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9683,7 +9719,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>146</v>
+        <v>537</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9701,10 +9737,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>166</v>
+        <v>539</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9715,46 +9751,42 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>535</v>
+        <v>85</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>536</v>
+        <v>163</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9802,19 +9834,19 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>538</v>
+        <v>165</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9835,7 +9867,7 @@
         <v>85</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9846,21 +9878,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9872,15 +9904,17 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>540</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>541</v>
+        <v>142</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9929,19 +9963,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>539</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -9959,10 +9993,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>544</v>
+        <v>85</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>545</v>
+        <v>166</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9973,42 +10007,46 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>540</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
       </c>
@@ -10062,13 +10100,13 @@
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10086,10 +10124,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>544</v>
+        <v>85</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>549</v>
+        <v>138</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10100,10 +10138,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10126,20 +10164,16 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>184</v>
+        <v>548</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10163,13 +10197,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10187,7 +10221,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10196,7 +10230,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>85</v>
+        <v>551</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10214,13 +10248,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>557</v>
+        <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>470</v>
+        <v>553</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10231,10 +10265,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10245,7 +10279,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10257,20 +10291,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>184</v>
+        <v>548</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10294,13 +10324,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>486</v>
+        <v>85</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>564</v>
+        <v>85</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>565</v>
+        <v>85</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10318,16 +10348,16 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>85</v>
+        <v>551</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10345,13 +10375,13 @@
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AQ62" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10362,10 +10392,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10388,17 +10418,19 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>567</v>
+        <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10423,13 +10455,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>85</v>
+        <v>564</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10447,7 +10479,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10474,13 +10506,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>85</v>
+        <v>566</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>571</v>
+        <v>478</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10491,10 +10523,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10505,7 +10537,7 @@
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>85</v>
@@ -10517,16 +10549,20 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10550,13 +10586,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>85</v>
+        <v>572</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>85</v>
+        <v>573</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10574,13 +10610,13 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>85</v>
@@ -10601,13 +10637,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>575</v>
+        <v>478</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10618,10 +10654,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10632,7 +10668,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10641,21 +10677,21 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10703,13 +10739,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10733,10 +10769,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10747,10 +10783,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10761,7 +10797,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10770,20 +10806,18 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>584</v>
+        <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>587</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10832,13 +10866,13 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -10862,10 +10896,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>581</v>
+        <v>552</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10876,10 +10910,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10902,20 +10936,18 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>524</v>
+        <v>585</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>593</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -10963,7 +10995,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -10993,10 +11025,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11007,10 +11039,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11021,7 +11053,7 @@
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
@@ -11030,18 +11062,20 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>162</v>
+        <v>592</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>163</v>
+        <v>593</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11090,19 +11124,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>165</v>
+        <v>591</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11120,10 +11154,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>85</v>
+        <v>589</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>166</v>
+        <v>596</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11141,7 +11175,7 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11157,21 +11191,23 @@
         <v>85</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>141</v>
+        <v>532</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>142</v>
+        <v>598</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>168</v>
+        <v>599</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11219,7 +11255,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>172</v>
+        <v>597</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11231,7 +11267,7 @@
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11249,10 +11285,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>85</v>
+        <v>602</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>166</v>
+        <v>603</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11263,46 +11299,42 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>535</v>
+        <v>85</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>536</v>
+        <v>163</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11350,19 +11382,19 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>538</v>
+        <v>165</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11383,7 +11415,7 @@
         <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11394,21 +11426,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11417,23 +11449,21 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>600</v>
+        <v>142</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>601</v>
+        <v>168</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11457,13 +11487,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>486</v>
+        <v>85</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>603</v>
+        <v>85</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11481,19 +11511,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>599</v>
+        <v>172</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11508,16 +11538,16 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>604</v>
+        <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>288</v>
+        <v>166</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>289</v>
+        <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
         <v>85</v>
@@ -11525,45 +11555,45 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>437</v>
+        <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>607</v>
+        <v>545</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>608</v>
+        <v>144</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>441</v>
+        <v>150</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11612,19 +11642,19 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>605</v>
+        <v>546</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11639,27 +11669,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>609</v>
+        <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>446</v>
+        <v>138</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11667,7 +11697,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>95</v>
@@ -11679,22 +11709,22 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>455</v>
+        <v>280</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11719,13 +11749,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>189</v>
+        <v>494</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>456</v>
+        <v>282</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11743,16 +11773,16 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>615</v>
+        <v>85</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>107</v>
@@ -11770,16 +11800,16 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>85</v>
+        <v>612</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>138</v>
+        <v>287</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>459</v>
+        <v>288</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>85</v>
+        <v>289</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>85</v>
@@ -11787,21 +11817,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11810,22 +11840,22 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>184</v>
+        <v>438</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>462</v>
+        <v>614</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>463</v>
+        <v>615</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>464</v>
+        <v>616</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11850,13 +11880,13 @@
         <v>85</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>466</v>
+        <v>85</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>467</v>
+        <v>85</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>85</v>
@@ -11874,13 +11904,13 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
@@ -11901,27 +11931,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>469</v>
+        <v>446</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>470</v>
+        <v>447</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>471</v>
+        <v>448</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11932,7 +11962,7 @@
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -11944,19 +11974,19 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>527</v>
+        <v>621</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>528</v>
+        <v>463</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -11981,13 +12011,13 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>85</v>
+        <v>622</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>85</v>
+        <v>464</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12005,16 +12035,16 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>85</v>
+        <v>623</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12035,20 +12065,282 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>530</v>
+        <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>531</v>
+        <v>467</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS75" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS76" t="s" s="2">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS77" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS75">
+  <autoFilter ref="A1:AS77">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12058,7 +12350,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI76">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="631">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,7 +671,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (63.05-.001)</t>
+    <t>1476: source value based on MICROBIOLOGY - IEN (63.05-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -901,10 +901,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lompo-49-1528:63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-: if NULL then http://loinc.org#42807-8 "Parasite identified in Isolate" {null}</t>
-  </si>
-  <si>
-    <t>1528: fixed value = http://loinc.org#42807-8 "Parasite identified in Isolate" when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case NULL</t>
+lompo-49-1528:If (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) is NULL then fixed value http://loinc.org#42807-8 "Parasite identified in Isolate" {null}</t>
+  </si>
+  <si>
+    <t>1528: fixed value = http://loinc.org#42807-8 "Parasite identified in Isolate" when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if NULL</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -953,7 +953,11 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lompo-49-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+  </si>
+  <si>
+    <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -987,10 +991,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lompo-49-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
+lompo-49-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -1035,7 +1039,11 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1480-2: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lompo-49-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+  </si>
+  <si>
+    <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1059,7 +1067,11 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1480-3: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lompo-49-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+  </si>
+  <si>
+    <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1139,7 +1151,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>844: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1271,7 +1283,7 @@
 </t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
+    <t>1450: source value based on MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
@@ -1293,7 +1305,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
+    <t>1484: source value based on MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1353,7 +1365,7 @@
 </t>
   </si>
   <si>
-    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+    <t>1464: reference based on MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
@@ -1372,7 +1384,7 @@
 </t>
   </si>
   <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+    <t>1679: reference based on MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
@@ -1426,7 +1438,7 @@
     <t>valueString</t>
   </si>
   <si>
-    <t>1857: source value from MICROBIOLOGY - PARASITE &gt; PARASITE - PARASITE &gt; ETIOLOGY FIELD - NAME (63.05-16 &gt; 63.34-.01 &gt; 61.2-.01)</t>
+    <t>1857: source value based on MICROBIOLOGY - PARASITE &gt; PARASITE - PARASITE &gt; ETIOLOGY FIELD - NAME (63.05-16 &gt; 63.34-.01 &gt; 61.2-.01)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity</t>
@@ -1536,7 +1548,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1454: source value from MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
+    <t>1454: source value based on MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SpecimenComment</t>
@@ -1625,7 +1637,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
+    <t>1659: reference based on MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
@@ -5944,10 +5956,10 @@
         <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>107</v>
+        <v>300</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -5962,10 +5974,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5976,10 +5988,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6103,10 +6115,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6232,10 +6244,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6261,16 +6273,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6319,7 +6331,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6331,10 +6343,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6349,10 +6361,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6363,10 +6375,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6392,13 +6404,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6448,7 +6460,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6478,10 +6490,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6492,10 +6504,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6521,14 +6533,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6577,7 +6589,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6589,10 +6601,10 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6607,10 +6619,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6621,10 +6633,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6650,14 +6662,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6706,7 +6718,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6718,10 +6730,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>107</v>
+        <v>337</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6736,10 +6748,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6750,10 +6762,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6776,19 +6788,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6837,7 +6849,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6867,10 +6879,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6881,10 +6893,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6910,16 +6922,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6968,7 +6980,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -6998,10 +7010,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7012,10 +7024,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7038,19 +7050,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7099,7 +7111,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7114,28 +7126,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7143,10 +7155,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7169,16 +7181,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7228,7 +7240,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7261,10 +7273,10 @@
         <v>287</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7272,14 +7284,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7298,19 +7310,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7359,7 +7371,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7383,19 +7395,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7403,14 +7415,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7429,19 +7441,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7478,7 +7490,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7488,7 +7500,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7497,10 +7509,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7512,19 +7524,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7532,16 +7544,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7560,19 +7572,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7621,7 +7633,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7630,34 +7642,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7665,10 +7677,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7691,16 +7703,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7750,7 +7762,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7765,13 +7777,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7780,13 +7792,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7794,10 +7806,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7820,17 +7832,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7867,7 +7879,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7877,7 +7889,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7901,19 +7913,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7921,13 +7933,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7949,17 +7961,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8008,7 +8020,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8023,28 +8035,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8052,13 +8064,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8080,17 +8092,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8139,7 +8151,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8154,28 +8166,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8183,10 +8195,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8209,19 +8221,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8258,7 +8270,7 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8268,7 +8280,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8277,10 +8289,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8295,30 +8307,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8343,16 +8355,16 @@
         <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8401,7 +8413,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8410,48 +8422,48 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AR47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS47" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>85</v>
@@ -8473,19 +8485,19 @@
         <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8534,7 +8546,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8543,13 +8555,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8561,30 +8573,30 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>85</v>
@@ -8609,16 +8621,16 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8667,7 +8679,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8676,13 +8688,13 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8694,27 +8706,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8740,16 +8752,16 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8778,7 +8790,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8796,7 +8808,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8805,13 +8817,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8829,7 +8841,7 @@
         <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8840,14 +8852,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8869,16 +8881,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8906,10 +8918,10 @@
         <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8927,7 +8939,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8954,27 +8966,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8997,19 +9009,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9058,7 +9070,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9073,10 +9085,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9088,10 +9100,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9102,10 +9114,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9131,13 +9143,13 @@
         <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9163,13 +9175,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9187,7 +9199,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9214,27 +9226,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9260,16 +9272,16 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9294,13 +9306,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9318,7 +9330,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9348,10 +9360,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9362,10 +9374,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9388,16 +9400,16 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9447,7 +9459,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9462,39 +9474,39 @@
         <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9517,16 +9529,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9576,7 +9588,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9603,27 +9615,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9646,19 +9658,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9707,7 +9719,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9719,7 +9731,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9737,10 +9749,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9751,10 +9763,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9878,10 +9890,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10007,14 +10019,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10036,10 +10048,10 @@
         <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>144</v>
@@ -10094,7 +10106,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10138,10 +10150,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10164,13 +10176,13 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10221,7 +10233,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10230,7 +10242,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10251,10 +10263,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10265,10 +10277,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10291,13 +10303,13 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10348,7 +10360,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10357,7 +10369,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10378,10 +10390,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10392,10 +10404,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10421,16 +10433,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10458,10 +10470,10 @@
         <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10479,7 +10491,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10506,13 +10518,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10523,10 +10535,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10552,16 +10564,16 @@
         <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10586,13 +10598,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10610,7 +10622,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10637,13 +10649,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10654,10 +10666,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10680,17 +10692,17 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10739,7 +10751,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10772,7 +10784,7 @@
         <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10783,10 +10795,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10812,10 +10824,10 @@
         <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10866,7 +10878,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10896,10 +10908,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10910,10 +10922,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10936,16 +10948,16 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10995,7 +11007,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11025,10 +11037,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11039,10 +11051,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11065,16 +11077,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11124,7 +11136,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11154,10 +11166,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11168,10 +11180,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11194,19 +11206,19 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11255,7 +11267,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11285,10 +11297,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11299,10 +11311,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11426,10 +11438,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11555,14 +11567,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11584,10 +11596,10 @@
         <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>144</v>
@@ -11642,7 +11654,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11686,10 +11698,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11715,13 +11727,13 @@
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>280</v>
@@ -11749,10 +11761,10 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="Z73" t="s" s="2">
         <v>282</v>
@@ -11773,7 +11785,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>95</v>
@@ -11800,7 +11812,7 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>287</v>
@@ -11817,10 +11829,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11843,19 +11855,19 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11904,7 +11916,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -11931,27 +11943,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11977,16 +11989,16 @@
         <v>184</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12014,10 +12026,10 @@
         <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12035,7 +12047,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12044,7 +12056,7 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12068,7 +12080,7 @@
         <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12079,14 +12091,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12108,16 +12120,16 @@
         <v>184</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12145,10 +12157,10 @@
         <v>189</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12166,7 +12178,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12193,27 +12205,27 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12239,16 +12251,16 @@
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12297,7 +12309,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12327,10 +12339,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3224" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="632">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -798,6 +798,9 @@
   </si>
   <si>
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_LabObservationStatus](ConceptMap-VF-LabObservationStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
@@ -5144,9 +5147,11 @@
       <c r="X22" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>85</v>
@@ -5179,28 +5184,28 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -5208,10 +5213,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5237,16 +5242,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -5256,7 +5261,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5274,16 +5279,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5293,7 +5298,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5308,7 +5313,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5326,10 +5331,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5337,13 +5342,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5368,16 +5373,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5387,7 +5392,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5405,10 +5410,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5426,7 +5431,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5459,10 +5464,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5470,14 +5475,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5499,16 +5504,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5536,10 +5541,10 @@
         <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5557,7 +5562,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5569,10 +5574,10 @@
         <v>85</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>85</v>
@@ -5581,30 +5586,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5728,10 +5733,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5857,10 +5862,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5883,19 +5888,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5944,7 +5949,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5956,10 +5961,10 @@
         <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -5974,10 +5979,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -5988,10 +5993,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6115,10 +6120,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6244,10 +6249,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6273,16 +6278,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6331,7 +6336,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6343,10 +6348,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6361,10 +6366,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6375,10 +6380,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6404,13 +6409,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6460,7 +6465,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6490,10 +6495,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6504,10 +6509,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6533,14 +6538,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6589,7 +6594,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6601,10 +6606,10 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6619,10 +6624,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6633,10 +6638,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6662,14 +6667,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6718,7 +6723,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6730,10 +6735,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6748,10 +6753,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6762,10 +6767,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6788,19 +6793,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6849,7 +6854,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6879,10 +6884,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6893,10 +6898,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6922,16 +6927,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -6980,7 +6985,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -7010,10 +7015,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7024,10 +7029,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7050,19 +7055,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7111,7 +7116,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7126,28 +7131,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7155,10 +7160,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7181,16 +7186,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7240,7 +7245,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7270,13 +7275,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7284,14 +7289,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7310,19 +7315,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7371,7 +7376,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7395,19 +7400,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7415,14 +7420,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7441,19 +7446,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7490,7 +7495,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7500,7 +7505,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7509,10 +7514,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7524,19 +7529,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7544,16 +7549,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7572,19 +7577,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7633,7 +7638,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7642,34 +7647,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7677,10 +7682,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7703,16 +7708,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7762,7 +7767,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7777,13 +7782,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7792,13 +7797,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7806,10 +7811,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7832,17 +7837,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7879,7 +7884,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7889,7 +7894,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7913,19 +7918,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7933,13 +7938,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -7961,17 +7966,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8020,7 +8025,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8035,28 +8040,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8064,13 +8069,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8092,17 +8097,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8151,7 +8156,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8166,28 +8171,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8195,10 +8200,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8221,19 +8226,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8270,7 +8275,7 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8280,7 +8285,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8289,10 +8294,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8307,30 +8312,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8355,16 +8360,16 @@
         <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8413,7 +8418,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8422,13 +8427,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8440,30 +8445,30 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>85</v>
@@ -8485,19 +8490,19 @@
         <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8546,7 +8551,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8555,13 +8560,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8573,30 +8578,30 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>85</v>
@@ -8621,16 +8626,16 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8679,7 +8684,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8688,13 +8693,13 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8706,27 +8711,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8752,16 +8757,16 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8790,7 +8795,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8808,7 +8813,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8817,13 +8822,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8841,7 +8846,7 @@
         <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8852,14 +8857,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8881,16 +8886,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8918,10 +8923,10 @@
         <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8939,7 +8944,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8966,27 +8971,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9009,19 +9014,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9070,7 +9075,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9085,10 +9090,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9100,10 +9105,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9114,10 +9119,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9143,13 +9148,13 @@
         <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9175,13 +9180,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9199,7 +9204,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9226,27 +9231,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9272,16 +9277,16 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9306,13 +9311,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9330,7 +9335,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9360,10 +9365,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9374,10 +9379,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9400,16 +9405,16 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9459,7 +9464,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9474,39 +9479,39 @@
         <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9529,16 +9534,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9588,7 +9593,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9615,27 +9620,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9658,19 +9663,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9719,7 +9724,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9731,7 +9736,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9749,10 +9754,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9763,10 +9768,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9890,10 +9895,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10019,14 +10024,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10048,10 +10053,10 @@
         <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>144</v>
@@ -10106,7 +10111,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10150,10 +10155,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10176,13 +10181,13 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10233,7 +10238,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10242,7 +10247,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10263,10 +10268,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10277,10 +10282,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10303,13 +10308,13 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10360,7 +10365,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10369,7 +10374,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10390,10 +10395,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10404,10 +10409,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10433,16 +10438,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10470,10 +10475,10 @@
         <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10491,7 +10496,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10518,13 +10523,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10535,10 +10540,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10564,16 +10569,16 @@
         <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10598,13 +10603,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10622,7 +10627,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10649,13 +10654,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10666,10 +10671,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10692,17 +10697,17 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10751,7 +10756,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10784,7 +10789,7 @@
         <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10795,10 +10800,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10824,10 +10829,10 @@
         <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10878,7 +10883,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10908,10 +10913,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10922,10 +10927,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10948,16 +10953,16 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11007,7 +11012,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11037,10 +11042,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11051,10 +11056,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11077,16 +11082,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11136,7 +11141,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11166,10 +11171,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11180,10 +11185,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11206,19 +11211,19 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11267,7 +11272,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11297,10 +11302,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11311,10 +11316,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11438,10 +11443,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11567,14 +11572,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11596,10 +11601,10 @@
         <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>144</v>
@@ -11654,7 +11659,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11698,10 +11703,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11727,16 +11732,16 @@
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11761,13 +11766,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11785,7 +11790,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>95</v>
@@ -11812,16 +11817,16 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>85</v>
@@ -11829,10 +11834,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11855,19 +11860,19 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11916,7 +11921,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -11943,27 +11948,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11989,16 +11994,16 @@
         <v>184</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12026,10 +12031,10 @@
         <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12047,7 +12052,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12056,7 +12061,7 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12080,7 +12085,7 @@
         <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12091,14 +12096,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12120,16 +12125,16 @@
         <v>184</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12157,10 +12162,10 @@
         <v>189</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12178,7 +12183,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12205,27 +12210,27 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12251,16 +12256,16 @@
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12309,7 +12314,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12339,10 +12344,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -904,7 +904,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lompo-49-1528:If (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) is NULL then fixed value http://loinc.org#42807-8 "Parasite identified in Isolate" {null}</t>
+lompo-49-1528:If (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) is NULL then fixed value http://loinc.org#42807-8 "Parasite identified in Isolate" {true}</t>
   </si>
   <si>
     <t>1528: fixed value = http://loinc.org#42807-8 "Parasite identified in Isolate" when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if NULL</t>
@@ -957,7 +957,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lompo-49-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+lompo-49-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {true}</t>
   </si>
   <si>
     <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
@@ -994,7 +994,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lompo-49-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+lompo-49-1480-1:If Not NULL then fixed value http://loinc.org {true}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
@@ -1043,7 +1043,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lompo-49-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+lompo-49-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {true}</t>
   </si>
   <si>
     <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
@@ -1071,7 +1071,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lompo-49-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+lompo-49-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {true}</t>
   </si>
   <si>
     <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3139" uniqueCount="625">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -843,6 +843,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -853,29 +875,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1444,28 +1444,6 @@
     <t>1857: source value based on MICROBIOLOGY - PARASITE &gt; PARASITE - PARASITE &gt; ETIOLOGY FIELD - NAME (63.05-16 &gt; 63.34-.01 &gt; 61.2-.01)</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>2099: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>2100: target not supported</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1627,7 +1605,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyParasitologySpecimen)
 </t>
   </si>
   <si>
@@ -2312,12 +2290,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS77"/>
+  <dimension ref="A1:AS75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5261,7 +5239,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>267</v>
+        <v>85</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5279,16 +5257,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5313,28 +5291,28 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5342,13 +5320,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>262</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5392,7 +5370,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5410,10 +5388,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5446,7 +5424,7 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>85</v>
+        <v>275</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>85</v>
@@ -5464,10 +5442,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -8465,11 +8443,9 @@
         <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8487,22 +8463,22 @@
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="N48" t="s" s="2">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8527,13 +8503,11 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8551,7 +8525,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8560,13 +8534,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8578,64 +8552,62 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>449</v>
+        <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>450</v>
+        <v>138</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8660,13 +8632,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>85</v>
+        <v>472</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8684,22 +8656,22 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>448</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>462</v>
+        <v>85</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8711,27 +8683,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>452</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8742,7 +8714,7 @@
         <v>83</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>96</v>
@@ -8754,19 +8726,19 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>184</v>
+        <v>478</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>464</v>
+        <v>479</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>466</v>
+        <v>481</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>467</v>
+        <v>482</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8791,11 +8763,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>468</v>
+        <v>85</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8813,25 +8787,25 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>469</v>
+        <v>85</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>85</v>
+        <v>484</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>85</v>
@@ -8843,10 +8817,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>138</v>
+        <v>485</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8857,21 +8831,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>473</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8886,17 +8860,15 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8920,13 +8892,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>189</v>
+        <v>491</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8944,13 +8916,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -8971,27 +8943,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>483</v>
+        <v>497</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9002,10 +8974,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -9014,19 +8986,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>485</v>
+        <v>184</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9051,13 +9023,13 @@
         <v>85</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>85</v>
+        <v>491</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>85</v>
+        <v>503</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>85</v>
@@ -9075,13 +9047,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9090,10 +9062,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>490</v>
+        <v>85</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>491</v>
+        <v>85</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9105,10 +9077,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9119,10 +9091,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9136,7 +9108,7 @@
         <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>85</v>
@@ -9145,16 +9117,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>508</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9180,13 +9152,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>499</v>
+        <v>85</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9204,7 +9176,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9219,39 +9191,39 @@
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>85</v>
+        <v>512</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>85</v>
+        <v>513</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>504</v>
+        <v>518</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9274,20 +9246,18 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>520</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>523</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9311,13 +9281,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>510</v>
+        <v>85</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9335,7 +9305,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9362,27 +9332,27 @@
         <v>85</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>85</v>
+        <v>524</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9393,10 +9363,10 @@
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9405,18 +9375,20 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9464,54 +9436,54 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>534</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>520</v>
+        <v>85</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>522</v>
+        <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>525</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9534,17 +9506,15 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>527</v>
+        <v>162</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>528</v>
+        <v>163</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9593,7 +9563,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>526</v>
+        <v>165</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9605,7 +9575,7 @@
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9620,31 +9590,31 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>531</v>
+        <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>532</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>533</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>534</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9663,20 +9633,18 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>536</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>537</v>
+        <v>142</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>538</v>
+        <v>168</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9724,7 +9692,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>535</v>
+        <v>172</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9736,7 +9704,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>541</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9754,10 +9722,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>542</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>543</v>
+        <v>166</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9768,42 +9736,46 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>85</v>
+        <v>540</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>163</v>
+        <v>541</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9851,19 +9823,19 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>165</v>
+        <v>543</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9884,7 +9856,7 @@
         <v>85</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9895,21 +9867,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9921,17 +9893,15 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>141</v>
+        <v>545</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>142</v>
+        <v>546</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>547</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9980,19 +9950,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>172</v>
+        <v>544</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>548</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -10010,10 +9980,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>166</v>
+        <v>550</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10024,46 +9994,42 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>141</v>
+        <v>545</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>85</v>
       </c>
@@ -10111,19 +10077,19 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>85</v>
+        <v>548</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10141,10 +10107,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>138</v>
+        <v>554</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10155,10 +10121,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10181,16 +10147,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>552</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10214,13 +10184,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>560</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10238,7 +10208,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10247,7 +10217,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10265,13 +10235,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>562</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>557</v>
+        <v>475</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10282,10 +10252,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10296,7 +10266,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10308,16 +10278,20 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>552</v>
+        <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10341,13 +10315,13 @@
         <v>85</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>85</v>
+        <v>491</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>85</v>
+        <v>569</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>85</v>
@@ -10365,16 +10339,16 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10392,13 +10366,13 @@
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>85</v>
+        <v>562</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>561</v>
+        <v>475</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10409,10 +10383,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10435,19 +10409,17 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>184</v>
+        <v>572</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10472,13 +10444,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>568</v>
+        <v>85</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10496,7 +10468,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10523,13 +10495,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>569</v>
+        <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>570</v>
+        <v>85</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>482</v>
+        <v>576</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10540,10 +10512,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10554,7 +10526,7 @@
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>85</v>
@@ -10566,20 +10538,16 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10603,37 +10571,37 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>576</v>
+        <v>85</v>
       </c>
       <c r="Z64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="AA64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>571</v>
-      </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>85</v>
@@ -10654,13 +10622,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>569</v>
+        <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>482</v>
+        <v>580</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10671,10 +10639,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10685,7 +10653,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10694,21 +10662,21 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10756,13 +10724,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10786,10 +10754,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>586</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10800,10 +10768,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10814,7 +10782,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10823,18 +10791,20 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>162</v>
+        <v>589</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>592</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10883,13 +10853,13 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -10913,10 +10883,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>556</v>
+        <v>586</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10927,10 +10897,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10953,18 +10923,20 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>589</v>
+        <v>529</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>598</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -11012,7 +10984,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11042,10 +11014,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11056,10 +11028,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11070,7 +11042,7 @@
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>85</v>
@@ -11079,20 +11051,18 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>596</v>
+        <v>162</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>597</v>
+        <v>163</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11141,19 +11111,19 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>595</v>
+        <v>165</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11171,10 +11141,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>593</v>
+        <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>600</v>
+        <v>166</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11185,14 +11155,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11208,23 +11178,21 @@
         <v>85</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>536</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>602</v>
+        <v>142</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>603</v>
+        <v>168</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>605</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11272,7 +11240,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>601</v>
+        <v>172</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11284,7 +11252,7 @@
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11302,10 +11270,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>606</v>
+        <v>85</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>607</v>
+        <v>166</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11316,42 +11284,46 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>85</v>
+        <v>540</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>163</v>
+        <v>541</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11399,19 +11371,19 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>165</v>
+        <v>543</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11432,7 +11404,7 @@
         <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11443,21 +11415,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11466,21 +11438,23 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>142</v>
+        <v>605</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>168</v>
+        <v>606</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>607</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11504,13 +11478,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>85</v>
+        <v>491</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>85</v>
+        <v>608</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11528,19 +11502,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>172</v>
+        <v>604</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11555,16 +11529,16 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>85</v>
+        <v>609</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>85</v>
+        <v>288</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>166</v>
+        <v>289</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="AS71" t="s" s="2">
         <v>85</v>
@@ -11579,38 +11553,38 @@
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>141</v>
+        <v>442</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>548</v>
+        <v>611</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>549</v>
+        <v>612</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>144</v>
+        <v>613</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>150</v>
+        <v>446</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11659,19 +11633,19 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>550</v>
+        <v>610</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11686,27 +11660,27 @@
         <v>85</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>85</v>
+        <v>450</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>138</v>
+        <v>451</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>85</v>
+        <v>452</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11714,7 +11688,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>95</v>
@@ -11726,22 +11700,22 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>281</v>
+        <v>460</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11766,40 +11740,40 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>498</v>
+        <v>189</v>
       </c>
       <c r="Y73" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF73" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="AG73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>85</v>
+        <v>620</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>107</v>
@@ -11817,16 +11791,16 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>616</v>
+        <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>288</v>
+        <v>138</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>289</v>
+        <v>464</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>290</v>
+        <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>85</v>
@@ -11834,21 +11808,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11857,22 +11831,22 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>442</v>
+        <v>184</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>618</v>
+        <v>467</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>619</v>
+        <v>468</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>620</v>
+        <v>469</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -11897,13 +11871,13 @@
         <v>85</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>85</v>
+        <v>472</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>85</v>
@@ -11921,13 +11895,13 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
@@ -11948,19 +11922,19 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>621</v>
+        <v>473</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>452</v>
+        <v>476</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -11979,7 +11953,7 @@
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -11991,7 +11965,7 @@
         <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="L75" t="s" s="2">
         <v>623</v>
@@ -12000,10 +11974,10 @@
         <v>624</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>625</v>
+        <v>532</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>467</v>
+        <v>533</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12028,13 +12002,13 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>626</v>
+        <v>85</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>468</v>
+        <v>85</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12058,10 +12032,10 @@
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>627</v>
+        <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12082,282 +12056,20 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>138</v>
+        <v>535</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>471</v>
+        <v>536</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS76" t="s" s="2">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS77" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS77">
+  <autoFilter ref="A1:AS75">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12367,7 +12079,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI76">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
